--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -160,12 +160,6 @@
   </si>
   <si>
     <t>1405/06/18</t>
-  </si>
-  <si>
-    <t>1405/06/21</t>
-  </si>
-  <si>
-    <t>دنگ کشمش</t>
   </si>
 </sst>
 </file>
@@ -653,7 +647,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>580000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1170,23 +1164,17 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>580000</v>
-      </c>
-      <c r="B37" s="6">
-        <v>430000</v>
-      </c>
+        <v>150000</v>
+      </c>
+      <c r="B37" s="6"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>580000</v>
+        <v>150000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1196,7 +1184,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>580000</v>
+        <v>150000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1206,7 +1194,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>580000</v>
+        <v>150000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1216,7 +1204,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>580000</v>
+        <v>150000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1226,7 +1214,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>2443000</v>
+        <v>2013000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1238,7 +1226,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>580000</v>
+        <v>150000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>دنگ مزخ پل ذوآب</t>
   </si>
 </sst>
 </file>
@@ -647,7 +653,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>150000</v>
+        <v>339000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,17 +1170,23 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
-      <c r="B37" s="6"/>
+        <v>339000</v>
+      </c>
+      <c r="B37" s="6">
+        <v>189000</v>
+      </c>
       <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="10"/>
+      <c r="D37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>339000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1184,7 +1196,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>339000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1194,7 +1206,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>339000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1204,7 +1216,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>339000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1214,7 +1226,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>2013000</v>
+        <v>2202000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1226,7 +1238,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>150000</v>
+        <v>339000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>دنگ مزخ پل ذوآب</t>
+  </si>
+  <si>
+    <t>1405/07/24</t>
   </si>
 </sst>
 </file>
@@ -653,7 +656,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>339000</v>
+        <v>519000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1186,17 +1189,23 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>339000</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>519000</v>
+      </c>
+      <c r="B38" s="6">
+        <v>180000</v>
+      </c>
       <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="10"/>
+      <c r="D38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>339000</v>
+        <v>519000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1206,7 +1215,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>339000</v>
+        <v>519000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1216,7 +1225,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>339000</v>
+        <v>519000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1226,7 +1235,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>2202000</v>
+        <v>2382000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1238,7 +1247,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>339000</v>
+        <v>519000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>1405/07/24</t>
+  </si>
+  <si>
+    <t>1405/07/29</t>
   </si>
 </sst>
 </file>
@@ -656,7 +659,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>519000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1205,17 +1208,23 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6">
         <v>519000</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="10"/>
+      <c r="D39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>519000</v>
+        <v>0</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1225,7 +1234,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>519000</v>
+        <v>0</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1239,7 +1248,7 @@
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
-        <v>1863000</v>
+        <v>2382000</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -1247,7 +1256,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>519000</v>
+        <v>0</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="53">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>1405/07/29</t>
+  </si>
+  <si>
+    <t>1405/08/07</t>
+  </si>
+  <si>
+    <t>دنگ ودکا</t>
   </si>
 </sst>
 </file>
@@ -659,7 +665,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>0</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1224,17 +1230,23 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="B40" s="6"/>
+        <v>125000</v>
+      </c>
+      <c r="B40" s="6">
+        <v>125000</v>
+      </c>
       <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="10"/>
+      <c r="D40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1244,7 +1256,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>2382000</v>
+        <v>2507000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1256,7 +1268,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>
